--- a/salidas/empresas/WDC.xlsx
+++ b/salidas/empresas/WDC.xlsx
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.73264598846436</v>
+        <v>11.73264694213867</v>
       </c>
       <c r="C4" t="n">
         <v>14.68631935119629</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.70483207702637</v>
+        <v>12.70483303070068</v>
       </c>
       <c r="C5" t="n">
         <v>15.90324974060059</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.28817844390869</v>
+        <v>12.28818035125732</v>
       </c>
       <c r="C6" t="n">
         <v>15.3817081451416</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.96210289001465</v>
+        <v>11.9621057510376</v>
       </c>
       <c r="C7" t="n">
         <v>14.97354507446289</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59138488769531</v>
+        <v>10.59138584136963</v>
       </c>
       <c r="C8" t="n">
         <v>13.25774765014648</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>11.05030536651611</v>
+        <v>11.0503044128418</v>
       </c>
       <c r="C9" t="n">
         <v>13.832200050354</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>10.92953300476074</v>
+        <v>10.92953681945801</v>
       </c>
       <c r="C10" t="n">
         <v>13.68102836608887</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.03822803497314</v>
+        <v>11.0382251739502</v>
       </c>
       <c r="C11" t="n">
         <v>13.81708240509033</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>11.83529567718506</v>
+        <v>11.83529663085938</v>
       </c>
       <c r="C14" t="n">
         <v>14.81481456756592</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.57564449310303</v>
+        <v>11.57564640045166</v>
       </c>
       <c r="C15" t="n">
         <v>14.48979568481445</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.15057945251465</v>
+        <v>10.15058040618896</v>
       </c>
       <c r="C16" t="n">
         <v>12.70597076416016</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.67592430114746</v>
+        <v>10.67592144012451</v>
       </c>
       <c r="C17" t="n">
         <v>13.36356830596924</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.35826301574707</v>
+        <v>11.35826396942139</v>
       </c>
       <c r="C18" t="n">
         <v>14.21768665313721</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>11.68433856964111</v>
+        <v>11.68433666229248</v>
       </c>
       <c r="C19" t="n">
         <v>14.62584972381592</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.89202308654785</v>
+        <v>12.89202117919922</v>
       </c>
       <c r="C20" t="n">
         <v>16.13756561279297</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.10574340820312</v>
+        <v>14.10574245452881</v>
       </c>
       <c r="C21" t="n">
         <v>17.65684127807617</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.28927898406982</v>
+        <v>15.28927230834961</v>
       </c>
       <c r="C22" t="n">
         <v>19.1383228302002</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.65158081054688</v>
+        <v>15.65157794952393</v>
       </c>
       <c r="C23" t="n">
         <v>19.59183692932129</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>16.68414688110352</v>
+        <v>16.68414306640625</v>
       </c>
       <c r="C24" t="n">
         <v>20.88435363769531</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.9716157913208</v>
+        <v>15.97161865234375</v>
       </c>
       <c r="C26" t="n">
         <v>19.99244117736816</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.64058685302734</v>
+        <v>18.64059829711914</v>
       </c>
       <c r="C27" t="n">
         <v>23.33333206176758</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>16.32788467407227</v>
+        <v>16.32787704467773</v>
       </c>
       <c r="C28" t="n">
         <v>20.43839836120605</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>22.66218185424805</v>
+        <v>22.66217994689941</v>
       </c>
       <c r="C30" t="n">
         <v>28.36734771728516</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>20.85065841674805</v>
+        <v>20.85065460205078</v>
       </c>
       <c r="C31" t="n">
         <v>26.09977340698242</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.38460731506348</v>
+        <v>17.38460540771484</v>
       </c>
       <c r="C32" t="n">
         <v>21.76114845275879</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>16.46072387695312</v>
+        <v>16.46072578430176</v>
       </c>
       <c r="C33" t="n">
         <v>20.60468673706055</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>12.87390422821045</v>
+        <v>12.87390327453613</v>
       </c>
       <c r="C34" t="n">
         <v>16.11488914489746</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.366871356964111</v>
+        <v>7.36686897277832</v>
       </c>
       <c r="C36" t="n">
         <v>9.221466064453125</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>6.913989543914795</v>
+        <v>6.913989067077637</v>
       </c>
       <c r="C37" t="n">
         <v>8.654573440551758</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.864398956298828</v>
+        <v>8.864396095275879</v>
       </c>
       <c r="C38" t="n">
         <v>11.0959939956665</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>11.67829895019531</v>
+        <v>11.67830181121826</v>
       </c>
       <c r="C40" t="n">
         <v>14.6182918548584</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.20235729217529</v>
+        <v>14.20236206054688</v>
       </c>
       <c r="C41" t="n">
         <v>17.77777862548828</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.00546741485596</v>
+        <v>15.00547313690186</v>
       </c>
       <c r="C42" t="n">
         <v>18.7830696105957</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>16.00180816650391</v>
+        <v>16.00180244445801</v>
       </c>
       <c r="C43" t="n">
         <v>20.03023338317871</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.26621055603027</v>
+        <v>18.26620864868164</v>
       </c>
       <c r="C44" t="n">
         <v>22.86470031738281</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.6997013092041</v>
+        <v>20.69969367980957</v>
       </c>
       <c r="C45" t="n">
         <v>25.91080856323242</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>22.05834007263184</v>
+        <v>22.05833435058594</v>
       </c>
       <c r="C46" t="n">
         <v>27.61148834228516</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>20.33739471435547</v>
+        <v>20.33738708496094</v>
       </c>
       <c r="C47" t="n">
         <v>25.45729446411133</v>
@@ -1378,7 +1378,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.24552536010742</v>
+        <v>22.24553489685059</v>
       </c>
       <c r="C48" t="n">
         <v>27.84580421447754</v>
@@ -1403,7 +1403,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>26.65960884094238</v>
+        <v>26.65961265563965</v>
       </c>
       <c r="C49" t="n">
         <v>33.37112426757812</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.93994522094727</v>
+        <v>22.93995094299316</v>
       </c>
       <c r="C50" t="n">
         <v>28.71504211425781</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>23.3264102935791</v>
+        <v>23.32640838623047</v>
       </c>
       <c r="C51" t="n">
         <v>29.19879150390625</v>
@@ -1478,7 +1478,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.54379081726074</v>
+        <v>23.54378700256348</v>
       </c>
       <c r="C52" t="n">
         <v>29.47089958190918</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.81185531616211</v>
+        <v>24.81185722351074</v>
       </c>
       <c r="C53" t="n">
         <v>31.05820083618164</v>
@@ -1528,7 +1528,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.01973152160645</v>
+        <v>21.01973342895508</v>
       </c>
       <c r="C54" t="n">
         <v>26.3114128112793</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>18.21186828613281</v>
+        <v>18.21186447143555</v>
       </c>
       <c r="C55" t="n">
         <v>22.79667472839355</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.93538284301758</v>
+        <v>15.93538379669189</v>
       </c>
       <c r="C56" t="n">
         <v>19.94709014892578</v>
@@ -1603,7 +1603,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.58881855010986</v>
+        <v>14.58881664276123</v>
       </c>
       <c r="C57" t="n">
         <v>18.26152610778809</v>
@@ -1632,7 +1632,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.14306640625</v>
+        <v>17.14306449890137</v>
       </c>
       <c r="C58" t="n">
         <v>21.45880508422852</v>
@@ -1661,7 +1661,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>19.32897186279297</v>
+        <v>19.32897567749023</v>
       </c>
       <c r="C59" t="n">
         <v>24.19501113891602</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.22869682312012</v>
+        <v>20.22870254516602</v>
       </c>
       <c r="C60" t="n">
         <v>25.32123947143555</v>
@@ -1719,7 +1719,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.47023963928223</v>
+        <v>20.47023582458496</v>
       </c>
       <c r="C61" t="n">
         <v>25.62358283996582</v>
@@ -1748,7 +1748,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.54270172119141</v>
+        <v>20.54269981384277</v>
       </c>
       <c r="C62" t="n">
         <v>25.71428680419922</v>
@@ -1777,7 +1777,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>18.46547889709473</v>
+        <v>18.46548271179199</v>
       </c>
       <c r="C63" t="n">
         <v>23.1141357421875</v>
@@ -1806,7 +1806,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>22.51726341247559</v>
+        <v>22.51725769042969</v>
       </c>
       <c r="C64" t="n">
         <v>28.18594169616699</v>
@@ -1835,7 +1835,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.03289794921875</v>
+        <v>24.03289985656738</v>
       </c>
       <c r="C65" t="n">
         <v>30.08314323425293</v>
@@ -1864,7 +1864,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>22.13080215454102</v>
+        <v>22.13080024719238</v>
       </c>
       <c r="C66" t="n">
         <v>27.70219230651855</v>
@@ -1951,7 +1951,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.80728912353516</v>
+        <v>17.80728721618652</v>
       </c>
       <c r="C69" t="n">
         <v>22.29024887084961</v>
@@ -1980,7 +1980,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.53081130981445</v>
+        <v>15.53081226348877</v>
       </c>
       <c r="C70" t="n">
         <v>19.44066429138184</v>
@@ -2009,7 +2009,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>16.08634185791016</v>
+        <v>16.08634376525879</v>
       </c>
       <c r="C71" t="n">
         <v>20.13605308532715</v>
@@ -2038,7 +2038,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.55367851257324</v>
+        <v>17.55368041992188</v>
       </c>
       <c r="C72" t="n">
         <v>21.9727897644043</v>
@@ -2067,7 +2067,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.68890380859375</v>
+        <v>18.68889999389648</v>
       </c>
       <c r="C73" t="n">
         <v>23.39380264282227</v>
@@ -2096,7 +2096,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.94964408874512</v>
+        <v>21.94965171813965</v>
       </c>
       <c r="C74" t="n">
         <v>27.47543525695801</v>
@@ -2125,7 +2125,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>23.7007884979248</v>
+        <v>23.70079231262207</v>
       </c>
       <c r="C75" t="n">
         <v>29.66742324829102</v>
@@ -2154,7 +2154,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>24.99301338195801</v>
+        <v>24.99300384521484</v>
       </c>
       <c r="C76" t="n">
         <v>31.28495788574219</v>
@@ -2183,7 +2183,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.43509864807129</v>
+        <v>23.43509674072266</v>
       </c>
       <c r="C77" t="n">
         <v>29.3348445892334</v>
@@ -2212,7 +2212,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>18.95458984375</v>
+        <v>18.95459747314453</v>
       </c>
       <c r="C78" t="n">
         <v>23.72637939453125</v>
@@ -2270,7 +2270,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.01479339599609</v>
+        <v>24.01478004455566</v>
       </c>
       <c r="C80" t="n">
         <v>30.06046867370605</v>
@@ -2299,7 +2299,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.25266456604004</v>
+        <v>25.25266647338867</v>
       </c>
       <c r="C81" t="n">
         <v>31.60997772216797</v>
@@ -2386,7 +2386,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.31451797485352</v>
+        <v>20.31451225280762</v>
       </c>
       <c r="C84" t="n">
         <v>25.26832962036133</v>
@@ -2415,7 +2415,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>25.99030303955078</v>
+        <v>25.99030876159668</v>
       </c>
       <c r="C85" t="n">
         <v>32.11640167236328</v>
@@ -2444,7 +2444,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.74897766113281</v>
+        <v>28.74897956848145</v>
       </c>
       <c r="C86" t="n">
         <v>35.52532196044922</v>
@@ -2473,7 +2473,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.84685707092285</v>
+        <v>28.84685325622559</v>
       </c>
       <c r="C87" t="n">
         <v>35.64625930786133</v>
@@ -2502,7 +2502,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>30.92408180236816</v>
+        <v>30.92406463623047</v>
       </c>
       <c r="C88" t="n">
         <v>38.01209259033203</v>
@@ -2531,7 +2531,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>33.99250793457031</v>
+        <v>33.99250030517578</v>
       </c>
       <c r="C89" t="n">
         <v>41.7838249206543</v>
@@ -2589,7 +2589,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>38.33966445922852</v>
+        <v>38.33965301513672</v>
       </c>
       <c r="C91" t="n">
         <v>46.93121719360352</v>
@@ -2618,7 +2618,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>39.75369644165039</v>
+        <v>39.75369262695312</v>
       </c>
       <c r="C92" t="n">
         <v>48.66213226318359</v>
@@ -2647,7 +2647,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>38.28408432006836</v>
+        <v>38.28407669067383</v>
       </c>
       <c r="C93" t="n">
         <v>46.86318969726562</v>
@@ -2705,7 +2705,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.1603889465332</v>
+        <v>43.160400390625</v>
       </c>
       <c r="C95" t="n">
         <v>52.63038635253906</v>
@@ -2734,7 +2734,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>46.5138053894043</v>
+        <v>46.51381683349609</v>
       </c>
       <c r="C96" t="n">
         <v>56.71957778930664</v>
@@ -2763,7 +2763,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>52.19522094726562</v>
+        <v>52.19521713256836</v>
       </c>
       <c r="C97" t="n">
         <v>63.41647720336914</v>
@@ -2821,7 +2821,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>54.1175422668457</v>
+        <v>54.11753845214844</v>
       </c>
       <c r="C99" t="n">
         <v>65.7520751953125</v>
@@ -2908,7 +2908,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>54.83565521240234</v>
+        <v>54.83564758300781</v>
       </c>
       <c r="C102" t="n">
         <v>66.40211486816406</v>
@@ -2937,7 +2937,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>57.86877059936523</v>
+        <v>57.8687858581543</v>
       </c>
       <c r="C103" t="n">
         <v>69.76568603515625</v>
@@ -2966,7 +2966,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>62.62742233276367</v>
+        <v>62.62740707397461</v>
       </c>
       <c r="C104" t="n">
         <v>75.50264739990234</v>
@@ -2995,7 +2995,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>64.58357238769531</v>
+        <v>64.58352661132812</v>
       </c>
       <c r="C105" t="n">
         <v>77.86092376708984</v>
@@ -3024,7 +3024,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>61.01612091064453</v>
+        <v>61.01611328125</v>
       </c>
       <c r="C106" t="n">
         <v>73.56008911132812</v>
@@ -3053,7 +3053,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>61.9289665222168</v>
+        <v>61.92896270751953</v>
       </c>
       <c r="C107" t="n">
         <v>74.35374450683594</v>
@@ -3082,7 +3082,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.01380157470703</v>
+        <v>65.01374053955078</v>
       </c>
       <c r="C108" t="n">
         <v>78.05744171142578</v>
@@ -3111,7 +3111,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>69.93881225585938</v>
+        <v>69.93882751464844</v>
       </c>
       <c r="C109" t="n">
         <v>83.67346954345703</v>
@@ -3140,7 +3140,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>61.42864227294922</v>
+        <v>61.42864990234375</v>
       </c>
       <c r="C110" t="n">
         <v>73.4920654296875</v>
@@ -3169,7 +3169,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>67.58855438232422</v>
+        <v>67.58858489990234</v>
       </c>
       <c r="C111" t="n">
         <v>80.86167907714844</v>
@@ -3227,7 +3227,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>62.08489227294922</v>
+        <v>62.08489608764648</v>
       </c>
       <c r="C113" t="n">
         <v>73.87754821777344</v>
@@ -3256,7 +3256,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>61.84352493286133</v>
+        <v>61.8435173034668</v>
       </c>
       <c r="C114" t="n">
         <v>73.59032440185547</v>
@@ -3285,7 +3285,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.11849975585938</v>
+        <v>50.11850357055664</v>
       </c>
       <c r="C115" t="n">
         <v>59.27437591552734</v>
@@ -3314,7 +3314,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>55.00124740600586</v>
+        <v>55.00125503540039</v>
       </c>
       <c r="C116" t="n">
         <v>65.04913330078125</v>
@@ -3343,7 +3343,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>52.38092422485352</v>
+        <v>52.38092041015625</v>
       </c>
       <c r="C117" t="n">
         <v>61.95011138916016</v>
@@ -3372,7 +3372,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>51.13897705078125</v>
+        <v>51.13897323608398</v>
       </c>
       <c r="C118" t="n">
         <v>60.04534912109375</v>
@@ -3401,7 +3401,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.01493453979492</v>
+        <v>43.01493072509766</v>
       </c>
       <c r="C119" t="n">
         <v>50.50642395019531</v>
@@ -3430,7 +3430,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>40.17602920532227</v>
+        <v>40.17603302001953</v>
       </c>
       <c r="C120" t="n">
         <v>47.17309188842773</v>
@@ -3488,7 +3488,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.14506340026855</v>
+        <v>31.14506912231445</v>
       </c>
       <c r="C122" t="n">
         <v>36.26606369018555</v>
@@ -3517,7 +3517,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>28.25644683837891</v>
+        <v>28.25644874572754</v>
       </c>
       <c r="C123" t="n">
         <v>32.90249252319336</v>
@@ -3546,7 +3546,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>30.98532867431641</v>
+        <v>30.9853401184082</v>
       </c>
       <c r="C124" t="n">
         <v>35.70672607421875</v>
@@ -3575,7 +3575,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>26.80717277526855</v>
+        <v>26.80716514587402</v>
       </c>
       <c r="C125" t="n">
         <v>30.89191246032715</v>
@@ -3604,7 +3604,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>30.52618980407715</v>
+        <v>30.52619552612305</v>
       </c>
       <c r="C126" t="n">
         <v>35.17762756347656</v>
@@ -3633,7 +3633,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>31.35385894775391</v>
+        <v>31.35385513305664</v>
       </c>
       <c r="C127" t="n">
         <v>35.72184371948242</v>
@@ -3662,7 +3662,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>31.51971054077148</v>
+        <v>31.51971435546875</v>
       </c>
       <c r="C128" t="n">
         <v>35.91080856323242</v>
@@ -3691,7 +3691,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>30.96242904663086</v>
+        <v>30.96243858337402</v>
       </c>
       <c r="C129" t="n">
         <v>35.27588653564453</v>
@@ -3720,7 +3720,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>39.12329483032227</v>
+        <v>39.12328720092773</v>
       </c>
       <c r="C130" t="n">
         <v>44.19501113891602</v>
@@ -3778,7 +3778,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>42.59599304199219</v>
+        <v>42.59601211547852</v>
       </c>
       <c r="C132" t="n">
         <v>48.11791229248047</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>51.81092071533203</v>
+        <v>51.81091690063477</v>
       </c>
       <c r="C135" t="n">
         <v>58.11035537719727</v>
@@ -3886,7 +3886,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>55.96592330932617</v>
+        <v>55.96591567993164</v>
       </c>
       <c r="C136" t="n">
         <v>62.38095092773438</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>61.07222747802734</v>
+        <v>61.07221603393555</v>
       </c>
       <c r="C138" t="n">
         <v>68.07256317138672</v>
@@ -3967,7 +3967,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>60.4109992980957</v>
+        <v>60.41100692749023</v>
       </c>
       <c r="C139" t="n">
         <v>66.96900939941406</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>58.03820419311523</v>
+        <v>58.03821182250977</v>
       </c>
       <c r="C140" t="n">
         <v>64.338623046875</v>
@@ -4021,7 +4021,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>60.18599700927734</v>
+        <v>60.18600845336914</v>
       </c>
       <c r="C141" t="n">
         <v>66.71957397460938</v>
@@ -4050,7 +4050,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>59.24484252929688</v>
+        <v>59.24485397338867</v>
       </c>
       <c r="C142" t="n">
         <v>65.30612182617188</v>
@@ -4079,7 +4079,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>61.21281433105469</v>
+        <v>61.21282958984375</v>
       </c>
       <c r="C143" t="n">
         <v>67.47543334960938</v>
@@ -4108,7 +4108,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>54.07464218139648</v>
+        <v>54.07464599609375</v>
       </c>
       <c r="C144" t="n">
         <v>59.60695266723633</v>
@@ -4137,7 +4137,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>54.87295150756836</v>
+        <v>54.87295913696289</v>
       </c>
       <c r="C145" t="n">
         <v>60.11338043212891</v>
@@ -4166,7 +4166,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>61.39312362670898</v>
+        <v>61.39312744140625</v>
       </c>
       <c r="C146" t="n">
         <v>67.25623321533203</v>
@@ -4282,7 +4282,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>57.93325805664062</v>
+        <v>57.93325424194336</v>
       </c>
       <c r="C150" t="n">
         <v>63.1216926574707</v>
@@ -4311,7 +4311,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>54.05113220214844</v>
+        <v>54.05112457275391</v>
       </c>
       <c r="C151" t="n">
         <v>58.51095962524414</v>
@@ -4340,7 +4340,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>48.98187637329102</v>
+        <v>48.98187255859375</v>
       </c>
       <c r="C152" t="n">
         <v>53.02343368530273</v>
@@ -4369,7 +4369,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>44.1569938659668</v>
+        <v>44.15700531005859</v>
       </c>
       <c r="C153" t="n">
         <v>47.80045318603516</v>
@@ -4398,7 +4398,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>41.2249755859375</v>
+        <v>41.22497940063477</v>
       </c>
       <c r="C154" t="n">
         <v>44.24792098999023</v>
@@ -4427,7 +4427,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.3307056427002</v>
+        <v>30.33070373535156</v>
       </c>
       <c r="C155" t="n">
         <v>32.5547981262207</v>
@@ -4456,7 +4456,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>31.96449851989746</v>
+        <v>31.96449279785156</v>
       </c>
       <c r="C156" t="n">
         <v>34.30839157104492</v>
@@ -4485,7 +4485,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>26.39230155944824</v>
+        <v>26.39229774475098</v>
       </c>
       <c r="C157" t="n">
         <v>27.94406700134277</v>
@@ -4514,7 +4514,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>32.11765670776367</v>
+        <v>32.11764907836914</v>
       </c>
       <c r="C158" t="n">
         <v>34.00604629516602</v>
@@ -4543,7 +4543,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.90837860107422</v>
+        <v>35.90838241577148</v>
       </c>
       <c r="C159" t="n">
         <v>38.0196533203125</v>
@@ -4572,7 +4572,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>34.69150924682617</v>
+        <v>34.69151306152344</v>
       </c>
       <c r="C160" t="n">
         <v>36.32653045654297</v>
@@ -4601,7 +4601,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>36.90034484863281</v>
+        <v>36.90033340454102</v>
       </c>
       <c r="C161" t="n">
         <v>38.63945770263672</v>
@@ -4659,7 +4659,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>34.71698760986328</v>
+        <v>34.71698379516602</v>
       </c>
       <c r="C163" t="n">
         <v>35.94104385375977</v>
@@ -4688,7 +4688,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>39.34592437744141</v>
+        <v>39.34591674804688</v>
       </c>
       <c r="C164" t="n">
         <v>40.73318099975586</v>
@@ -4744,7 +4744,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>43.54409027099609</v>
+        <v>43.5440788269043</v>
       </c>
       <c r="C166" t="n">
         <v>45.07936477661133</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>37.07293701171875</v>
+        <v>37.07294464111328</v>
       </c>
       <c r="C168" t="n">
         <v>38.04232788085938</v>
@@ -4825,7 +4825,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>46.7518310546875</v>
+        <v>46.75182723999023</v>
       </c>
       <c r="C169" t="n">
         <v>47.97430038452148</v>
@@ -4879,7 +4879,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>41.25030517578125</v>
+        <v>41.25030899047852</v>
       </c>
       <c r="C171" t="n">
         <v>41.99546432495117</v>
@@ -4933,7 +4933,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>34.66006469726562</v>
+        <v>34.66006851196289</v>
       </c>
       <c r="C173" t="n">
         <v>34.82993316650391</v>
@@ -4960,7 +4960,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>33.37385177612305</v>
+        <v>33.37385940551758</v>
       </c>
       <c r="C174" t="n">
         <v>33.53741455078125</v>
@@ -4987,7 +4987,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>33.20837783813477</v>
+        <v>33.2083740234375</v>
       </c>
       <c r="C175" t="n">
         <v>33.37112426757812</v>
@@ -5014,7 +5014,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>32.41859817504883</v>
+        <v>32.41859436035156</v>
       </c>
       <c r="C176" t="n">
         <v>32.57747650146484</v>
@@ -5068,7 +5068,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>27.49187278747559</v>
+        <v>27.49187469482422</v>
       </c>
       <c r="C178" t="n">
         <v>27.62660598754883</v>
@@ -5095,7 +5095,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>28.37943840026855</v>
+        <v>28.37943649291992</v>
       </c>
       <c r="C179" t="n">
         <v>28.51851844787598</v>
@@ -5122,7 +5122,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>33.75746536254883</v>
+        <v>33.75746154785156</v>
       </c>
       <c r="C180" t="n">
         <v>33.92290115356445</v>
@@ -5149,7 +5149,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>41.66278839111328</v>
+        <v>41.66279220581055</v>
       </c>
       <c r="C181" t="n">
         <v>41.86697006225586</v>
@@ -5176,7 +5176,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>42.44504165649414</v>
+        <v>42.44504547119141</v>
       </c>
       <c r="C182" t="n">
         <v>42.65306091308594</v>
@@ -5257,7 +5257,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>53.12588119506836</v>
+        <v>53.12587738037109</v>
       </c>
       <c r="C185" t="n">
         <v>53.3862419128418</v>
@@ -5332,7 +5332,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.83850479125977</v>
+        <v>48.8385009765625</v>
       </c>
       <c r="C188" t="n">
         <v>49.07785415649414</v>
@@ -5357,7 +5357,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>47.53724670410156</v>
+        <v>47.5372428894043</v>
       </c>
       <c r="C189" t="n">
         <v>47.77021789550781</v>
@@ -5382,7 +5382,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>42.45257568359375</v>
+        <v>42.45256805419922</v>
       </c>
       <c r="C190" t="n">
         <v>42.66062164306641</v>
@@ -5407,7 +5407,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>39.3310546875</v>
+        <v>39.33105850219727</v>
       </c>
       <c r="C191" t="n">
         <v>39.52381134033203</v>
@@ -5432,7 +5432,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>43.505615234375</v>
+        <v>43.50561141967773</v>
       </c>
       <c r="C192" t="n">
         <v>43.71882247924805</v>
@@ -5461,7 +5461,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>49.04911041259766</v>
+        <v>49.04911804199219</v>
       </c>
       <c r="C193" t="n">
         <v>49.28949356079102</v>
@@ -5519,7 +5519,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>38.31562423706055</v>
+        <v>38.31562042236328</v>
       </c>
       <c r="C195" t="n">
         <v>38.50340270996094</v>
@@ -5606,7 +5606,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>45.64929962158203</v>
+        <v>45.64929580688477</v>
       </c>
       <c r="C198" t="n">
         <v>45.87301635742188</v>
@@ -5664,7 +5664,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>36.93162536621094</v>
+        <v>36.93162155151367</v>
       </c>
       <c r="C200" t="n">
         <v>37.11262130737305</v>
@@ -5693,7 +5693,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>31.78677368164062</v>
+        <v>31.78677558898926</v>
       </c>
       <c r="C201" t="n">
         <v>31.94255447387695</v>
@@ -5722,7 +5722,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>24.48318481445312</v>
+        <v>24.48318672180176</v>
       </c>
       <c r="C202" t="n">
         <v>24.60317420959473</v>
@@ -5780,7 +5780,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>27.64230728149414</v>
+        <v>27.64230918884277</v>
       </c>
       <c r="C204" t="n">
         <v>27.77777862548828</v>
@@ -5838,7 +5838,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>33.05794525146484</v>
+        <v>33.05794906616211</v>
       </c>
       <c r="C206" t="n">
         <v>33.21995544433594</v>
@@ -6029,7 +6029,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>33.84772109985352</v>
+        <v>33.84772491455078</v>
       </c>
       <c r="C213" t="n">
         <v>34.01360321044922</v>
@@ -6056,7 +6056,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>34.32159805297852</v>
+        <v>34.32159423828125</v>
       </c>
       <c r="C214" t="n">
         <v>34.48979568481445</v>
@@ -6110,7 +6110,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>36.3374137878418</v>
+        <v>36.33740997314453</v>
       </c>
       <c r="C216" t="n">
         <v>36.51549530029297</v>
@@ -6137,7 +6137,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>39.39122772216797</v>
+        <v>39.39123153686523</v>
       </c>
       <c r="C217" t="n">
         <v>39.58427810668945</v>
@@ -6164,7 +6164,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>43.06182479858398</v>
+        <v>43.06182861328125</v>
       </c>
       <c r="C218" t="n">
         <v>43.27286529541016</v>
@@ -6191,7 +6191,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>44.73165130615234</v>
+        <v>44.73165512084961</v>
       </c>
       <c r="C219" t="n">
         <v>44.95087051391602</v>
@@ -6245,7 +6245,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>53.27631759643555</v>
+        <v>53.27631378173828</v>
       </c>
       <c r="C221" t="n">
         <v>53.53741455078125</v>
@@ -6272,7 +6272,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>56.63100051879883</v>
+        <v>56.63100814819336</v>
       </c>
       <c r="C222" t="n">
         <v>56.90854263305664</v>
@@ -6299,7 +6299,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>56.99204635620117</v>
+        <v>56.99205017089844</v>
       </c>
       <c r="C223" t="n">
         <v>57.27135467529297</v>
@@ -6326,7 +6326,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>50.43311309814453</v>
+        <v>50.43310928344727</v>
       </c>
       <c r="C224" t="n">
         <v>50.68027114868164</v>
@@ -6436,7 +6436,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>54.90100860595703</v>
+        <v>54.90100479125977</v>
       </c>
       <c r="C228" t="n">
         <v>55.17006683349609</v>
@@ -6494,7 +6494,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>48.98893737792969</v>
+        <v>48.98894119262695</v>
       </c>
       <c r="C230" t="n">
         <v>49.22902679443359</v>
@@ -6552,7 +6552,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>40.23282241821289</v>
+        <v>40.23282623291016</v>
       </c>
       <c r="C232" t="n">
         <v>40.43000030517578</v>
@@ -6639,7 +6639,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>63.79657363891602</v>
+        <v>63.79657745361328</v>
       </c>
       <c r="C235" t="n">
         <v>63.9900016784668</v>
@@ -6726,7 +6726,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>119.8364334106445</v>
+        <v>119.83642578125</v>
       </c>
       <c r="C238" t="n">
         <v>120.0599975585938</v>
@@ -6842,7 +6842,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>249.9648590087891</v>
+        <v>249.96484375</v>
       </c>
       <c r="C242" t="n">
         <v>250.2299957275391</v>
@@ -6871,7 +6871,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>279.4036254882812</v>
+        <v>279.4036560058594</v>
       </c>
       <c r="C243" t="n">
         <v>279.7000122070312</v>
